--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -186,21 +186,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>TEMAS DE FÍSICA</t>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
@@ -216,6 +213,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -234,24 +273,9 @@
     <t>ESPARZA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
     <t>LIMON</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -288,9 +312,6 @@
     <t>TIBURCIO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
@@ -324,12 +345,6 @@
     <t>BASILIO</t>
   </si>
   <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
@@ -360,9 +375,6 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>VERGEL</t>
   </si>
   <si>
@@ -393,27 +405,15 @@
     <t>AIDA</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
     <t>ODALYS</t>
   </si>
   <si>
     <t>KIMBERLY ALONDRA</t>
   </si>
   <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
     <t>MARIJOSE</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
     <t>GERMAN ERNESTO</t>
   </si>
   <si>
@@ -445,9 +445,6 @@
   </si>
   <si>
     <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -948,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -1002,7 +999,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1025,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -1079,7 +1076,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1102,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1156,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1179,7 +1176,7 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -1233,7 +1230,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1256,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -1310,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1333,7 +1330,7 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1387,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1410,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1464,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1487,7 +1484,7 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1541,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1564,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -1618,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1641,7 +1638,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>7</v>
@@ -1695,7 +1692,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1718,7 +1715,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>8</v>
@@ -1772,7 +1769,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1795,7 +1792,7 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -1849,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1949,7 +1946,7 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -2003,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2026,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2080,7 +2077,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2103,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -2157,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2180,7 +2177,7 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2234,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2257,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2311,7 +2308,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2334,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>9</v>
@@ -2388,7 +2385,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2411,7 +2408,7 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2465,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2488,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
         <v>8</v>
@@ -2542,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2565,7 +2562,7 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>8</v>
@@ -2619,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2642,7 +2639,7 @@
         <v>9</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>9</v>
@@ -2696,7 +2693,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2719,7 +2716,7 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -2773,7 +2770,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2796,7 +2793,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -2850,7 +2847,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2873,7 +2870,7 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>8</v>
@@ -2927,7 +2924,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2950,7 +2947,7 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -3004,7 +3001,7 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3027,7 +3024,7 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -3081,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3181,7 +3178,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -3235,7 +3232,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3255,7 +3252,7 @@
         <v>9</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G34">
         <v>6</v>
@@ -3291,7 +3288,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3421,7 +3418,7 @@
         <v>124</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>124</v>
@@ -3480,7 +3477,7 @@
         <v>116</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>116</v>
@@ -3539,7 +3536,7 @@
         <v>124</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>124</v>
@@ -3598,7 +3595,7 @@
         <v>124</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>124</v>
@@ -3657,7 +3654,7 @@
         <v>124</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>124</v>
@@ -3716,7 +3713,7 @@
         <v>124</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>120</v>
@@ -3775,7 +3772,7 @@
         <v>124</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>124</v>
@@ -3834,7 +3831,7 @@
         <v>124</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>124</v>
@@ -3893,7 +3890,7 @@
         <v>124</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>124</v>
@@ -3952,7 +3949,7 @@
         <v>120</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>120</v>
@@ -4011,7 +4008,7 @@
         <v>124</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>124</v>
@@ -4070,7 +4067,7 @@
         <v>124</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>124</v>
@@ -4129,7 +4126,7 @@
         <v>116</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>116</v>
@@ -4188,7 +4185,7 @@
         <v>124</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>124</v>
@@ -4247,7 +4244,7 @@
         <v>116</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>116</v>
@@ -4306,7 +4303,7 @@
         <v>124</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>116</v>
@@ -4365,7 +4362,7 @@
         <v>116</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>120</v>
@@ -4424,7 +4421,7 @@
         <v>124</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>124</v>
@@ -4483,7 +4480,7 @@
         <v>124</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>124</v>
@@ -4542,7 +4539,7 @@
         <v>116</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>116</v>
@@ -4601,7 +4598,7 @@
         <v>124</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>124</v>
@@ -4660,7 +4657,7 @@
         <v>124</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>124</v>
@@ -4719,7 +4716,7 @@
         <v>124</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>124</v>
@@ -4778,7 +4775,7 @@
         <v>124</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>124</v>
@@ -4837,7 +4834,7 @@
         <v>124</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>124</v>
@@ -4896,7 +4893,7 @@
         <v>124</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>124</v>
@@ -4955,7 +4952,7 @@
         <v>124</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>124</v>
@@ -5014,7 +5011,7 @@
         <v>124</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>124</v>
@@ -5073,7 +5070,7 @@
         <v>112</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>112</v>
@@ -5132,7 +5129,7 @@
         <v>124</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>124</v>
@@ -5188,7 +5185,7 @@
         <v>105</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>96</v>
@@ -5230,7 +5227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -5270,27 +5267,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>58.06</v>
+      </c>
+      <c r="G2">
+        <v>41.94</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5299,27 +5308,30 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>12.9</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5328,19 +5340,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>58.06</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G4">
-        <v>41.94</v>
+        <v>9.68</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5351,7 +5363,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5360,51 +5372,51 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>70.97</v>
+        <v>93.55</v>
       </c>
       <c r="G5">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>16.13</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5415,10 +5427,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -5442,38 +5454,6 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>30</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>8.1</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
         <v>0</v>
       </c>
     </row>
@@ -5484,7 +5464,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5493,16 +5473,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5513,19 +5493,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>18330051920393</v>
+        <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -5533,39 +5513,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920115</v>
+        <v>20330051920168</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920116</v>
+        <v>20330051920168</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>56</v>
@@ -5573,19 +5553,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920118</v>
+        <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>56</v>
@@ -5593,19 +5573,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920121</v>
+        <v>20330051920133</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>56</v>
@@ -5613,618 +5593,41 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920427</v>
+        <v>20330051920151</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920123</v>
+        <v>20330051920151</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920124</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920125</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920126</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920127</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920128</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920168</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920168</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920131</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920132</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920132</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920133</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920133</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920134</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920137</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920139</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920387</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920140</v>
-      </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>135</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920141</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920389</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920142</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920143</v>
-      </c>
-      <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920387</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920148</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920150</v>
-      </c>
-      <c r="B33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920151</v>
-      </c>
-      <c r="B34" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920151</v>
-      </c>
-      <c r="B35" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920153</v>
-      </c>
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920399</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
         <v>56</v>
       </c>
     </row>
@@ -6244,16 +5647,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>53</v>
@@ -6261,16 +5664,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920126</v>
+        <v>20330051920168</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -6278,16 +5681,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920168</v>
+        <v>20330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -6295,53 +5698,53 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920132</v>
+        <v>20330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920133</v>
+        <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920151</v>
+        <v>20330051920133</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6349,16 +5752,16 @@
         <v>18330051920393</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6366,16 +5769,16 @@
         <v>20330051920115</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6383,16 +5786,16 @@
         <v>20330051920116</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6400,16 +5803,16 @@
         <v>20330051920118</v>
       </c>
       <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
         <v>68</v>
       </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6417,16 +5820,16 @@
         <v>20330051920121</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6434,16 +5837,16 @@
         <v>19330051920427</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6451,16 +5854,16 @@
         <v>20330051920123</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6468,16 +5871,16 @@
         <v>20330051920124</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6485,16 +5888,16 @@
         <v>20330051920125</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6502,16 +5905,16 @@
         <v>20330051920127</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6519,16 +5922,16 @@
         <v>20330051920128</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6536,16 +5939,16 @@
         <v>20330051920131</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6553,16 +5956,16 @@
         <v>20330051920134</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6570,16 +5973,16 @@
         <v>20330051920137</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6587,16 +5990,16 @@
         <v>20330051920139</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6604,16 +6007,16 @@
         <v>19330051920387</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6621,16 +6024,16 @@
         <v>20330051920140</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6638,16 +6041,16 @@
         <v>20330051920141</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6655,16 +6058,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6672,16 +6075,16 @@
         <v>20330051920142</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6689,16 +6092,16 @@
         <v>20330051920143</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6706,16 +6109,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>135</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6723,16 +6126,16 @@
         <v>20330051920148</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6740,16 +6143,16 @@
         <v>20330051920150</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6757,13 +6160,13 @@
         <v>20330051920153</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6771,16 +6174,16 @@
         <v>19330051920399</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6790,7 +6193,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6799,16 +6202,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6822,19 +6225,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920393</v>
+        <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -6845,19 +6248,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920393</v>
+        <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -6868,45 +6271,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920115</v>
+        <v>20330051920127</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920115</v>
+        <v>20330051920127</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6914,45 +6317,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920116</v>
+        <v>20330051920387</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6960,45 +6363,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920118</v>
+        <v>18330051920393</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920118</v>
+        <v>20330051920115</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7006,45 +6409,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920121</v>
+        <v>20330051920118</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7052,25 +6455,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920124</v>
+        <v>20330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7078,19 +6481,19 @@
         <v>20330051920124</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7101,545 +6504,111 @@
         <v>20330051920125</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920125</v>
+        <v>20330051920133</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920133</v>
+        <v>20330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920133</v>
+        <v>20330051920148</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>56</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920137</v>
+        <v>20330051920153</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920137</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920148</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920148</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920153</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920153</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920427</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920123</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920128</v>
-      </c>
-      <c r="B26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920131</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920134</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920139</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920387</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920140</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920141</v>
-      </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920389</v>
-      </c>
-      <c r="B33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920142</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920143</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920150</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>19330051920399</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -195,12 +195,12 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -213,22 +213,112 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>HUESCA</t>
   </si>
   <si>
+    <t>LIMON</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
   </si>
   <si>
     <t>NOYOLA</t>
@@ -237,214 +327,124 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
     <t>ESMERALDA</t>
   </si>
   <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
     <t>ALDAIR OMAR</t>
   </si>
   <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ABDIEL</t>
   </si>
   <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>DIANA VIANNEY</t>
+  </si>
+  <si>
     <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -1629,7 +1629,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1869,7 +1869,7 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -1914,7 +1914,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1923,7 +1923,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -2068,7 +2068,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2091,7 +2091,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -2145,7 +2145,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -3092,7 +3092,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -3101,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F32">
         <v>6</v>
@@ -3146,7 +3146,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3155,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3940,7 +3940,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C13">
         <v>105</v>
@@ -4117,7 +4117,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="C16">
         <v>105</v>
@@ -4235,7 +4235,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>105</v>
@@ -4294,7 +4294,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>105</v>
@@ -5061,7 +5061,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C32">
         <v>105</v>
@@ -5308,25 +5308,25 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="G3">
-        <v>12.9</v>
+        <v>22.58</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5363,42 +5363,42 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -5427,16 +5427,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5464,7 +5464,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5489,146 +5489,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920126</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920168</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920151</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920151</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5664,98 +5524,98 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920168</v>
+        <v>18330051920393</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920151</v>
+        <v>20330051920115</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920126</v>
+        <v>20330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920132</v>
+        <v>20330051920118</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920133</v>
+        <v>20330051920121</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>18330051920393</v>
+        <v>19330051920427</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -5766,13 +5626,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920115</v>
+        <v>20330051920123</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -5783,13 +5643,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920116</v>
+        <v>20330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -5800,13 +5660,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920118</v>
+        <v>20330051920125</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -5817,13 +5677,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920121</v>
+        <v>20330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -5834,13 +5694,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920427</v>
+        <v>20330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -5851,13 +5711,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920123</v>
+        <v>20330051920128</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -5868,13 +5728,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920124</v>
+        <v>20330051920168</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -5885,13 +5745,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -5902,13 +5762,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920127</v>
+        <v>20330051920132</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -5919,13 +5779,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920128</v>
+        <v>20330051920133</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -5936,13 +5796,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920131</v>
+        <v>20330051920134</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -5953,13 +5813,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920134</v>
+        <v>20330051920137</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -5970,13 +5830,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920137</v>
+        <v>20330051920139</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -5987,13 +5847,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -6004,13 +5864,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -6021,13 +5881,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -6038,13 +5898,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -6055,13 +5915,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920389</v>
+        <v>20330051920142</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -6072,13 +5932,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -6089,16 +5949,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920143</v>
+        <v>20330051920387</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6106,16 +5966,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6123,13 +5983,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920148</v>
+        <v>20330051920150</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
@@ -6140,13 +6000,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920150</v>
+        <v>20330051920151</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -6160,7 +6020,7 @@
         <v>20330051920153</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -6174,10 +6034,10 @@
         <v>19330051920399</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>143</v>
@@ -6228,13 +6088,13 @@
         <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6243,7 +6103,7 @@
         <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -6251,13 +6111,13 @@
         <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6274,13 +6134,13 @@
         <v>20330051920127</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6297,13 +6157,13 @@
         <v>20330051920127</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6320,13 +6180,13 @@
         <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6343,13 +6203,13 @@
         <v>20330051920387</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6366,13 +6226,13 @@
         <v>18330051920393</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6389,13 +6249,13 @@
         <v>20330051920115</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6412,13 +6272,13 @@
         <v>20330051920116</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6435,13 +6295,13 @@
         <v>20330051920118</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6458,13 +6318,13 @@
         <v>20330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6481,13 +6341,13 @@
         <v>20330051920124</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6504,13 +6364,13 @@
         <v>20330051920125</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6524,16 +6384,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920133</v>
+        <v>20330051920137</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -6542,21 +6402,21 @@
         <v>56</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920137</v>
+        <v>20330051920148</v>
       </c>
       <c r="B16" t="s">
         <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -6570,22 +6430,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6596,7 +6456,7 @@
         <v>20330051920153</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>142</v>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -198,7 +198,7 @@
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>NC</t>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -213,6 +212,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -222,76 +224,25 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
     <t>ESPARZA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ZARATE</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>MARCELINO</t>
@@ -303,64 +254,19 @@
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
     <t>FERNANDEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>SALAZAR</t>
   </si>
   <si>
     <t>RAMON</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
+    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>TANIA</t>
@@ -372,91 +278,28 @@
     <t>AMARANTA DENISSE</t>
   </si>
   <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
     <t>VALENTIN</t>
   </si>
   <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
     <t>ODALYS</t>
   </si>
   <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
     <t>MEILYN ADABEL</t>
   </si>
   <si>
-    <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
     <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -509,11 +352,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,7 +798,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -969,7 +813,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -990,7 +834,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -1031,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1046,7 +890,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1108,7 +952,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1123,7 +967,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1144,7 +988,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1185,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1200,7 +1044,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1236,7 +1080,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1262,7 +1106,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1277,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1313,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1339,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1354,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1390,7 +1234,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1416,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1431,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1467,7 +1311,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1493,7 +1337,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1508,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1529,7 +1373,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1544,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1570,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1585,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1621,7 +1465,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1647,7 +1491,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1662,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1698,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1724,7 +1568,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1739,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1760,7 +1604,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1801,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1816,7 +1660,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1852,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1878,7 +1722,7 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1893,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1955,7 +1799,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1970,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1991,7 +1835,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2032,7 +1876,7 @@
         <v>4</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2047,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2109,7 +1953,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2124,7 +1968,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2160,7 +2004,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2186,7 +2030,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2201,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2237,7 +2081,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2263,7 +2107,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2278,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2299,7 +2143,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2314,7 +2158,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2340,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2355,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2376,7 +2220,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2417,7 +2261,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2432,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2468,7 +2312,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2494,7 +2338,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2509,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2545,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2571,7 +2415,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2586,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2622,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2648,7 +2492,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2663,7 +2507,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2684,7 +2528,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2699,7 +2543,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2725,7 +2569,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2740,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2776,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2802,7 +2646,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2817,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2853,7 +2697,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2879,7 +2723,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2894,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2915,7 +2759,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2956,7 +2800,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2971,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3007,7 +2851,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3033,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3048,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3084,7 +2928,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3110,7 +2954,7 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3125,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3146,7 +2990,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3187,7 +3031,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3202,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3258,7 +3102,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3267,7 +3111,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3282,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3427,7 +3271,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3442,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3486,7 +3330,7 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3501,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3545,7 +3389,7 @@
         <v>92</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3560,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3604,7 +3448,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3619,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3663,7 +3507,7 @@
         <v>84</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3678,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3722,7 +3566,7 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3737,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3781,7 +3625,7 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -3796,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3840,7 +3684,7 @@
         <v>96</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3855,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3899,7 +3743,7 @@
         <v>92</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3914,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3958,7 +3802,7 @@
         <v>64</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -3973,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4017,7 +3861,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4032,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4076,7 +3920,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4091,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4135,7 +3979,7 @@
         <v>80</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4150,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4194,7 +4038,7 @@
         <v>92</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4209,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4253,7 +4097,7 @@
         <v>84</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4268,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4312,7 +4156,7 @@
         <v>96</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4327,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4371,7 +4215,7 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4386,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4430,7 +4274,7 @@
         <v>96</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4445,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4489,7 +4333,7 @@
         <v>96</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4504,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4548,7 +4392,7 @@
         <v>96</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4563,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4607,7 +4451,7 @@
         <v>96</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4622,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4666,7 +4510,7 @@
         <v>80</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4681,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4725,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4740,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4784,7 +4628,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4799,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4843,7 +4687,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -4858,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4902,7 +4746,7 @@
         <v>96</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -4917,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4961,7 +4805,7 @@
         <v>92</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -4976,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5020,7 +4864,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5035,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5079,7 +4923,7 @@
         <v>92</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5094,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5138,7 +4982,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5153,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5191,7 +5035,7 @@
         <v>96</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5200,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5231,6 +5075,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5276,24 +5122,24 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>58.06</v>
-      </c>
-      <c r="G2">
-        <v>41.94</v>
+        <v>12</v>
+      </c>
+      <c r="F2" s="2">
+        <v>61.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>38.7</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5308,24 +5154,24 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>77.42</v>
-      </c>
-      <c r="G3">
-        <v>22.58</v>
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>16.1</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5345,11 +5191,11 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>90.31999999999999</v>
-      </c>
-      <c r="G4">
-        <v>9.68</v>
+      <c r="F4" s="2">
+        <v>90.3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="H4">
         <v>8.800000000000001</v>
@@ -5357,7 +5203,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5377,10 +5223,10 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
@@ -5389,7 +5235,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5409,10 +5255,10 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
@@ -5421,7 +5267,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5441,10 +5287,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
@@ -5453,7 +5299,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5498,562 +5344,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>18330051920393</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920116</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920118</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920121</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>19330051920427</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920123</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920124</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920125</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920127</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920128</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920131</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920132</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920133</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920134</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920137</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920139</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>19330051920387</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920140</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920141</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920389</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920142</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920143</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920387</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>20330051920148</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>20330051920150</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>20330051920151</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>20330051920153</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>19330051920399</v>
-      </c>
-      <c r="B32" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6085,16 +5376,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920126</v>
+        <v>20330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6108,22 +5399,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920126</v>
+        <v>20330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6131,22 +5422,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920127</v>
+        <v>18330051920393</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6154,16 +5445,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920127</v>
+        <v>20330051920115</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6177,22 +5468,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920387</v>
+        <v>20330051920116</v>
       </c>
       <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6200,16 +5491,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920387</v>
+        <v>19330051920427</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6223,16 +5514,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330051920393</v>
+        <v>20330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6246,16 +5537,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920115</v>
+        <v>20330051920140</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6269,16 +5560,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920116</v>
+        <v>20330051920387</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6292,22 +5583,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920118</v>
+        <v>20330051920148</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6315,16 +5606,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920121</v>
+        <v>20330051920153</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6333,141 +5621,6 @@
         <v>55</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920124</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920125</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920137</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920148</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920151</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920153</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -801,16 +801,16 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -837,16 +837,16 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -878,16 +878,16 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -914,16 +914,16 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -955,16 +955,16 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -994,13 +994,13 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>6</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1032,16 +1032,16 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1109,16 +1109,16 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>7</v>
@@ -1148,13 +1148,13 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1186,16 +1186,16 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1222,16 +1222,16 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1263,16 +1263,16 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1302,13 +1302,13 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1340,16 +1340,16 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1379,13 +1379,13 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1417,16 +1417,16 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -1456,13 +1456,13 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1494,16 +1494,16 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1533,13 +1533,13 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>6</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1571,16 +1571,16 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1607,16 +1607,16 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1648,16 +1648,16 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -1725,16 +1725,16 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1764,13 +1764,13 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1802,16 +1802,16 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1838,16 +1838,16 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1879,16 +1879,16 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -1956,16 +1956,16 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -1992,16 +1992,16 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2033,16 +2033,16 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>7</v>
@@ -2072,13 +2072,13 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2110,16 +2110,16 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -2149,13 +2149,13 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2187,16 +2187,16 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2226,13 +2226,13 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2264,16 +2264,16 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2300,16 +2300,16 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2341,16 +2341,16 @@
         <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2380,13 +2380,13 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2418,16 +2418,16 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2454,16 +2454,16 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2495,16 +2495,16 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2534,13 +2534,13 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2572,16 +2572,16 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2688,13 +2688,13 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2726,16 +2726,16 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2765,13 +2765,13 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2803,16 +2803,16 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -2839,16 +2839,16 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>6</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -2880,16 +2880,16 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -2957,16 +2957,16 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -2993,7 +2993,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -3034,16 +3034,16 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>6</v>
@@ -3073,13 +3073,13 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>7</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3105,7 +3105,7 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3129,7 +3129,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3274,16 +3274,16 @@
         <v>90</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M4">
         <v>104</v>
@@ -3333,16 +3333,16 @@
         <v>92.5</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M5">
         <v>116</v>
@@ -3392,16 +3392,16 @@
         <v>92.5</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M6">
         <v>108</v>
@@ -3451,16 +3451,16 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M7">
         <v>120</v>
@@ -3510,16 +3510,16 @@
         <v>92.5</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M8">
         <v>116</v>
@@ -3569,16 +3569,16 @@
         <v>97.5</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M9">
         <v>108</v>
@@ -3628,16 +3628,16 @@
         <v>97.5</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M10">
         <v>116</v>
@@ -3687,16 +3687,16 @@
         <v>87.5</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M11">
         <v>120</v>
@@ -3746,16 +3746,16 @@
         <v>92.5</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12">
         <v>112</v>
@@ -3805,16 +3805,16 @@
         <v>72.5</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -3864,16 +3864,16 @@
         <v>97.5</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M14">
         <v>116</v>
@@ -3923,16 +3923,16 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M15">
         <v>116</v>
@@ -3982,16 +3982,16 @@
         <v>70</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M16">
         <v>88</v>
@@ -4041,16 +4041,16 @@
         <v>90</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -4100,16 +4100,16 @@
         <v>67.5</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M18">
         <v>84</v>
@@ -4159,16 +4159,16 @@
         <v>80</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19">
         <v>104</v>
@@ -4218,16 +4218,16 @@
         <v>82.5</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20">
         <v>116</v>
@@ -4277,16 +4277,16 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M21">
         <v>116</v>
@@ -4336,16 +4336,16 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M22">
         <v>112</v>
@@ -4395,16 +4395,16 @@
         <v>95</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M23">
         <v>116</v>
@@ -4454,16 +4454,16 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M24">
         <v>108</v>
@@ -4513,16 +4513,16 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M25">
         <v>120</v>
@@ -4572,16 +4572,16 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M26">
         <v>120</v>
@@ -4631,16 +4631,16 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M27">
         <v>120</v>
@@ -4690,16 +4690,16 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M28">
         <v>120</v>
@@ -4749,16 +4749,16 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M29">
         <v>116</v>
@@ -4808,16 +4808,16 @@
         <v>72.5</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M30">
         <v>104</v>
@@ -4867,16 +4867,16 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M31">
         <v>116</v>
@@ -4926,16 +4926,16 @@
         <v>60</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M32">
         <v>116</v>
@@ -4985,16 +4985,16 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M33">
         <v>112</v>
@@ -5038,7 +5038,7 @@
         <v>90</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5262,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,7 +212,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>TORRES</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>BAUTISTA</t>
@@ -236,13 +236,10 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>RAMON</t>
   </si>
   <si>
     <t>MARCELINO</t>
@@ -263,10 +260,7 @@
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
+    <t>MEILYN ADABEL</t>
   </si>
   <si>
     <t>TANIA</t>
@@ -285,9 +279,6 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -807,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -884,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -961,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1038,7 +1029,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1115,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1151,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1192,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1228,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1269,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1305,7 +1296,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1346,7 +1337,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1423,7 +1414,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1459,7 +1450,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1500,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -1536,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1577,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1613,7 +1604,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1654,7 +1645,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1690,7 +1681,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1731,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -1767,7 +1758,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1808,7 +1799,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -1844,7 +1835,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -1885,7 +1876,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -1962,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -1998,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2039,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -2075,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2116,7 +2107,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -2193,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2270,7 +2261,7 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2347,7 +2338,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2424,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2501,7 +2492,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2578,7 +2569,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2655,7 +2646,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2691,7 +2682,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2732,7 +2723,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -2768,7 +2759,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2809,7 +2800,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -2845,7 +2836,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2886,7 +2877,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -2963,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -2999,7 +2990,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3040,7 +3031,7 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>9</v>
@@ -3108,7 +3099,7 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -3280,7 +3271,7 @@
         <v>116</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>120</v>
@@ -3339,7 +3330,7 @@
         <v>116</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>120</v>
@@ -3398,7 +3389,7 @@
         <v>116</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>120</v>
@@ -3457,7 +3448,7 @@
         <v>116</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>120</v>
@@ -3516,7 +3507,7 @@
         <v>116</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>120</v>
@@ -3575,7 +3566,7 @@
         <v>116</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>120</v>
@@ -3634,7 +3625,7 @@
         <v>116</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>120</v>
@@ -3693,7 +3684,7 @@
         <v>116</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>120</v>
@@ -3752,7 +3743,7 @@
         <v>116</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>120</v>
@@ -3811,7 +3802,7 @@
         <v>116</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>120</v>
@@ -3870,7 +3861,7 @@
         <v>116</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>120</v>
@@ -3929,7 +3920,7 @@
         <v>116</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>120</v>
@@ -3988,7 +3979,7 @@
         <v>116</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>120</v>
@@ -4047,7 +4038,7 @@
         <v>116</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>120</v>
@@ -4106,7 +4097,7 @@
         <v>116</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>120</v>
@@ -4165,7 +4156,7 @@
         <v>116</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>120</v>
@@ -4224,7 +4215,7 @@
         <v>116</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>120</v>
@@ -4283,7 +4274,7 @@
         <v>116</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>120</v>
@@ -4342,7 +4333,7 @@
         <v>116</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>120</v>
@@ -4401,7 +4392,7 @@
         <v>116</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>120</v>
@@ -4460,7 +4451,7 @@
         <v>116</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>120</v>
@@ -4519,7 +4510,7 @@
         <v>116</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>120</v>
@@ -4578,7 +4569,7 @@
         <v>116</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>120</v>
@@ -4637,7 +4628,7 @@
         <v>116</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>120</v>
@@ -4696,7 +4687,7 @@
         <v>116</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>120</v>
@@ -4755,7 +4746,7 @@
         <v>116</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>120</v>
@@ -4814,7 +4805,7 @@
         <v>116</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>120</v>
@@ -4873,7 +4864,7 @@
         <v>116</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>120</v>
@@ -4932,7 +4923,7 @@
         <v>116</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>120</v>
@@ -4991,7 +4982,7 @@
         <v>116</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>120</v>
@@ -5041,7 +5032,7 @@
         <v>105</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>92</v>
@@ -5177,7 +5168,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5186,19 +5177,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>90.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>9.699999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5209,28 +5200,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>90.3</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5241,10 +5232,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -5273,16 +5264,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5294,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5344,7 +5335,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5376,16 +5367,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920151</v>
+        <v>20330051920148</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5399,22 +5390,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920151</v>
+        <v>20330051920148</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5428,10 +5419,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -5451,10 +5442,10 @@
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5474,10 +5465,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5497,10 +5488,10 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5523,7 +5514,7 @@
         <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5543,10 +5534,10 @@
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5566,10 +5557,10 @@
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -5583,44 +5574,21 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920148</v>
+        <v>20330051920153</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920153</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -3247,55 +3247,55 @@
         <v>97.5</v>
       </c>
       <c r="C4">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="I4">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>92.7</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3306,55 +3306,55 @@
         <v>82.5</v>
       </c>
       <c r="C5">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="E5">
         <v>100</v>
       </c>
       <c r="F5">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="G5">
         <v>92</v>
       </c>
       <c r="H5">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="I5">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>120</v>
+        <v>96.7</v>
       </c>
       <c r="M5">
-        <v>116</v>
+        <v>94.5</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3365,16 +3365,16 @@
         <v>92.5</v>
       </c>
       <c r="C6">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>92</v>
@@ -3383,37 +3383,37 @@
         <v>92.5</v>
       </c>
       <c r="I6">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>108</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3424,16 +3424,16 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -3442,37 +3442,37 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3483,55 +3483,55 @@
         <v>95</v>
       </c>
       <c r="C8">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
       </c>
       <c r="F8">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>84</v>
       </c>
       <c r="H8">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="I8">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>116</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3542,55 +3542,55 @@
         <v>92.5</v>
       </c>
       <c r="C9">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D9">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9">
-        <v>120</v>
+        <v>96.8</v>
       </c>
       <c r="G9">
         <v>92</v>
       </c>
       <c r="H9">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="I9">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>120</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M9">
-        <v>108</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3601,16 +3601,16 @@
         <v>97.5</v>
       </c>
       <c r="C10">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
       </c>
       <c r="F10">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>92</v>
@@ -3619,37 +3619,37 @@
         <v>97.5</v>
       </c>
       <c r="I10">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>116</v>
+        <v>94.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3660,55 +3660,55 @@
         <v>95</v>
       </c>
       <c r="C11">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
       </c>
       <c r="F11">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>96</v>
       </c>
       <c r="H11">
-        <v>87.5</v>
+        <v>91.3</v>
       </c>
       <c r="I11">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>120</v>
+        <v>98.2</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3719,55 +3719,55 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>92</v>
       </c>
       <c r="H12">
-        <v>92.5</v>
+        <v>91.3</v>
       </c>
       <c r="I12">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>112</v>
+        <v>92.7</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3778,55 +3778,55 @@
         <v>67.5</v>
       </c>
       <c r="C13">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>96.8</v>
       </c>
       <c r="E13">
         <v>100</v>
       </c>
       <c r="F13">
-        <v>120</v>
+        <v>96.8</v>
       </c>
       <c r="G13">
         <v>64</v>
       </c>
       <c r="H13">
-        <v>72.5</v>
+        <v>70</v>
       </c>
       <c r="I13">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>120</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>74.5</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3837,55 +3837,55 @@
         <v>77.5</v>
       </c>
       <c r="C14">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D14">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14">
-        <v>97.5</v>
+        <v>87.5</v>
       </c>
       <c r="I14">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3896,55 +3896,55 @@
         <v>97.5</v>
       </c>
       <c r="C15">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D15">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I15">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3955,55 +3955,55 @@
         <v>77.5</v>
       </c>
       <c r="C16">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D16">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="E16">
         <v>100</v>
       </c>
       <c r="F16">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="G16">
         <v>80</v>
       </c>
       <c r="H16">
-        <v>70</v>
+        <v>73.8</v>
       </c>
       <c r="I16">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>120</v>
+        <v>96.7</v>
       </c>
       <c r="M16">
-        <v>88</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4014,55 +4014,55 @@
         <v>92.5</v>
       </c>
       <c r="C17">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>92</v>
       </c>
       <c r="H17">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="I17">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>87.3</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4073,55 +4073,55 @@
         <v>75</v>
       </c>
       <c r="C18">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="E18">
         <v>100</v>
       </c>
       <c r="F18">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="G18">
         <v>84</v>
       </c>
       <c r="H18">
-        <v>67.5</v>
+        <v>71.3</v>
       </c>
       <c r="I18">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>120</v>
+        <v>96.7</v>
       </c>
       <c r="M18">
-        <v>84</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>71.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4132,16 +4132,16 @@
         <v>80</v>
       </c>
       <c r="C19">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
       </c>
       <c r="F19">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="G19">
         <v>96</v>
@@ -4150,37 +4150,37 @@
         <v>80</v>
       </c>
       <c r="I19">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>120</v>
+        <v>96.7</v>
       </c>
       <c r="M19">
-        <v>104</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4191,55 +4191,55 @@
         <v>85</v>
       </c>
       <c r="C20">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>120</v>
+        <v>96.8</v>
       </c>
       <c r="G20">
         <v>92</v>
       </c>
       <c r="H20">
-        <v>82.5</v>
+        <v>83.8</v>
       </c>
       <c r="I20">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>120</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M20">
-        <v>116</v>
+        <v>94.5</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>83.8</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4250,55 +4250,55 @@
         <v>77.5</v>
       </c>
       <c r="C21">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D21">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
       </c>
       <c r="F21">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>96</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>88.8</v>
       </c>
       <c r="I21">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>116</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4309,16 +4309,16 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
       </c>
       <c r="F22">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>96</v>
@@ -4327,37 +4327,37 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>112</v>
+        <v>94.5</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4368,55 +4368,55 @@
         <v>92.5</v>
       </c>
       <c r="C23">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="E23">
         <v>100</v>
       </c>
       <c r="F23">
-        <v>116</v>
+        <v>93.5</v>
       </c>
       <c r="G23">
         <v>96</v>
       </c>
       <c r="H23">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="I23">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>120</v>
+        <v>96.7</v>
       </c>
       <c r="M23">
-        <v>116</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4427,55 +4427,55 @@
         <v>95</v>
       </c>
       <c r="C24">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>96</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I24">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>108</v>
+        <v>92.7</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4486,55 +4486,55 @@
         <v>97.5</v>
       </c>
       <c r="C25">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>80</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I25">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4545,16 +4545,16 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -4563,37 +4563,37 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4604,16 +4604,16 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D27">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
       </c>
       <c r="F27">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -4622,37 +4622,37 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4663,55 +4663,55 @@
         <v>97.5</v>
       </c>
       <c r="C28">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>100</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I28">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4722,55 +4722,55 @@
         <v>80</v>
       </c>
       <c r="C29">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
       </c>
       <c r="F29">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>96</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I29">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>116</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4781,55 +4781,55 @@
         <v>92.5</v>
       </c>
       <c r="C30">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D30">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
       </c>
       <c r="F30">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>92</v>
       </c>
       <c r="H30">
-        <v>72.5</v>
+        <v>82.5</v>
       </c>
       <c r="I30">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>104</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4840,16 +4840,16 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -4858,37 +4858,37 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4899,55 +4899,55 @@
         <v>65</v>
       </c>
       <c r="C32">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D32">
-        <v>112</v>
+        <v>90.3</v>
       </c>
       <c r="E32">
         <v>100</v>
       </c>
       <c r="F32">
-        <v>112</v>
+        <v>90.3</v>
       </c>
       <c r="G32">
         <v>92</v>
       </c>
       <c r="H32">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="I32">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>120</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M32">
-        <v>116</v>
+        <v>94.5</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4958,55 +4958,55 @@
         <v>95</v>
       </c>
       <c r="C33">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D33">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
       </c>
       <c r="F33">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I33">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>112</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5017,7 +5017,7 @@
         <v>95</v>
       </c>
       <c r="C34">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -5026,28 +5026,28 @@
         <v>96</v>
       </c>
       <c r="H34">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I34">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>92</v>
+        <v>85.5</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>85.5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -188,18 +188,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,76 +212,40 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
   </si>
 </sst>
 </file>
@@ -807,40 +771,40 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>8</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -884,28 +848,28 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -917,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -961,40 +925,40 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1038,25 +1002,25 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1115,22 +1079,22 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -1139,16 +1103,16 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1192,22 +1156,22 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1225,7 +1189,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1269,28 +1233,28 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1346,25 +1310,25 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1379,7 +1343,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1423,25 +1387,25 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1500,37 +1464,37 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1577,22 +1541,22 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1610,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1654,25 +1618,25 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1681,7 +1645,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1731,37 +1695,37 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1808,25 +1772,25 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1885,25 +1849,25 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -1912,7 +1876,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -1962,37 +1926,37 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2039,37 +2003,37 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2116,25 +2080,25 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2193,22 +2157,22 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2270,25 +2234,25 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2297,13 +2261,13 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2347,22 +2311,22 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2374,7 +2338,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2424,22 +2388,22 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2501,22 +2465,22 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2578,22 +2542,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2655,22 +2619,22 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2688,7 +2652,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2732,25 +2696,25 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2759,13 +2723,13 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2809,25 +2773,25 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -2836,13 +2800,13 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2886,22 +2850,22 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -2963,34 +2927,34 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>6</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3040,40 +3004,40 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>9</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3105,22 +3069,22 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3280,7 +3244,7 @@
         <v>92.7</v>
       </c>
       <c r="N4">
-        <v>93.8</v>
+        <v>85.8</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3295,7 +3259,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3339,22 +3303,22 @@
         <v>94.5</v>
       </c>
       <c r="N5">
-        <v>87.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3398,7 +3362,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N6">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3413,7 +3377,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3516,22 +3480,22 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N8">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
         <v>93.8</v>
-      </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
-      <c r="P8">
-        <v>100</v>
-      </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
-        <v>100</v>
-      </c>
-      <c r="S8">
-        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3575,7 +3539,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N9">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3587,10 +3551,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="S9">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3634,7 +3598,7 @@
         <v>94.5</v>
       </c>
       <c r="N10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3649,7 +3613,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3693,7 +3657,7 @@
         <v>98.2</v>
       </c>
       <c r="N11">
-        <v>91.3</v>
+        <v>89</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3708,7 +3672,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3752,7 +3716,7 @@
         <v>92.7</v>
       </c>
       <c r="N12">
-        <v>91.3</v>
+        <v>94.5</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3767,7 +3731,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>92.7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3811,22 +3775,22 @@
         <v>74.5</v>
       </c>
       <c r="N13">
-        <v>70</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>98.3</v>
+        <v>96.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="S13">
-        <v>74.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3870,7 +3834,7 @@
         <v>98.2</v>
       </c>
       <c r="N14">
-        <v>87.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3885,7 +3849,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3929,7 +3893,7 @@
         <v>98.2</v>
       </c>
       <c r="N15">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3944,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>98.2</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3988,22 +3952,22 @@
         <v>76.40000000000001</v>
       </c>
       <c r="N16">
+        <v>83.5</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>95</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>97.5</v>
+      </c>
+      <c r="S16">
         <v>73.8</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>96.7</v>
-      </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
-        <v>96.7</v>
-      </c>
-      <c r="S16">
-        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4047,7 +4011,7 @@
         <v>87.3</v>
       </c>
       <c r="N17">
-        <v>91.3</v>
+        <v>94.5</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4062,7 +4026,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>87.3</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4106,22 +4070,22 @@
         <v>76.40000000000001</v>
       </c>
       <c r="N18">
-        <v>71.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P18">
-        <v>96.7</v>
+        <v>91.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="S18">
-        <v>76.40000000000001</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4165,7 +4129,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N19">
-        <v>80</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4177,10 +4141,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="S19">
-        <v>90.90000000000001</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4224,22 +4188,22 @@
         <v>94.5</v>
       </c>
       <c r="N20">
-        <v>83.8</v>
+        <v>84.3</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>96.7</v>
+        <v>91.3</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="S20">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4283,7 +4247,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N21">
-        <v>88.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4298,7 +4262,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>96.40000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4357,7 +4321,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4401,22 +4365,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N23">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4460,7 +4424,7 @@
         <v>92.7</v>
       </c>
       <c r="N24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4475,7 +4439,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4519,7 +4483,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N25">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4534,7 +4498,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4696,7 +4660,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4755,7 +4719,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N29">
-        <v>90</v>
+        <v>93.7</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -4770,7 +4734,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4814,7 +4778,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N30">
-        <v>82.5</v>
+        <v>89</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -4829,7 +4793,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4888,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4932,22 +4896,22 @@
         <v>94.5</v>
       </c>
       <c r="N32">
-        <v>62.5</v>
+        <v>77.2</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
         <v>100</v>
       </c>
       <c r="R32">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="S32">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4991,22 +4955,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N33">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
         <v>97.5</v>
-      </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
-      <c r="P33">
-        <v>100</v>
-      </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
-        <v>100</v>
-      </c>
-      <c r="S33">
-        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5038,7 +5002,7 @@
         <v>85.5</v>
       </c>
       <c r="N34">
-        <v>92.5</v>
+        <v>89.8</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5047,7 +5011,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>85.5</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>
@@ -5113,19 +5077,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>61.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>38.7</v>
+        <v>12.9</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5136,7 +5100,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5145,19 +5109,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="G3" s="2">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5168,7 +5132,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5177,19 +5141,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>87.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="G4" s="2">
-        <v>12.9</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5200,28 +5164,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5232,10 +5196,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -5253,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5264,16 +5228,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5285,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5335,7 +5299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5367,19 +5331,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920148</v>
+        <v>20330051920132</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -5390,22 +5354,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920148</v>
+        <v>20330051920132</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5413,22 +5377,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920393</v>
+        <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5436,16 +5400,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920115</v>
+        <v>20330051920151</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5459,16 +5423,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>20330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5482,16 +5446,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920427</v>
+        <v>20330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5500,95 +5464,6 @@
         <v>55</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920127</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920387</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920153</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHV - Estadisticos 20222.xlsx
+++ b/grupos/6ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,37 +215,37 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
     <t>NOYOLA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
     <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
   </si>
 </sst>
 </file>
@@ -2945,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -4878,7 +4878,7 @@
         <v>92</v>
       </c>
       <c r="H32">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -4896,7 +4896,7 @@
         <v>94.5</v>
       </c>
       <c r="N32">
-        <v>77.2</v>
+        <v>85</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5132,28 +5132,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -5196,16 +5196,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5299,7 +5299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920151</v>
+        <v>20330051920126</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -5389,10 +5389,10 @@
         <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5400,16 +5400,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920151</v>
+        <v>20330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5423,16 +5423,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920126</v>
+        <v>20330051920151</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5441,29 +5441,6 @@
         <v>55</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920168</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>
